--- a/paper/tables/data_image_count_by_dataset.xlsx
+++ b/paper/tables/data_image_count_by_dataset.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Clustering-Validity\paper\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{78C37F71-FAD4-43F0-BB57-E8608091CC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A690E76A-4AC7-4A66-A3EE-F70FAB7EE15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3BCA12E5-AC9D-4263-B90C-94CC17E8C675}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BCA12E5-AC9D-4263-B90C-94CC17E8C675}"/>
   </bookViews>
   <sheets>
     <sheet name="data_image_count_by_dataset" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1004,9 +1017,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CC2D98-340F-4262-AF65-BD6C79FDBB20}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1049,23 +1062,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>217</v>
@@ -1074,26 +1087,26 @@
         <v>201</v>
       </c>
       <c r="G4">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="I4">
         <f>SUM(B4:D4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <f>SUM(E4:G4)</f>
-        <v>593</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1105,18 +1118,18 @@
         <v>143</v>
       </c>
       <c r="G5">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I37" si="0">SUM(B5:D5)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J37" si="1">SUM(E5:G5)</f>
-        <v>447</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1130,13 +1143,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F6">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="G6">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
@@ -1144,21 +1157,21 @@
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>96</v>
@@ -1167,29 +1180,29 @@
         <v>71</v>
       </c>
       <c r="G7">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
-        <v>321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>164</v>
@@ -1198,29 +1211,29 @@
         <v>71</v>
       </c>
       <c r="G8">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>389</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>147</v>
@@ -1229,29 +1242,29 @@
         <v>170</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>471</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>18</v>
@@ -1260,29 +1273,29 @@
         <v>110</v>
       </c>
       <c r="G10">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>222</v>
@@ -1291,29 +1304,29 @@
         <v>125</v>
       </c>
       <c r="G11">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>548</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>116</v>
@@ -1322,18 +1335,18 @@
         <v>149</v>
       </c>
       <c r="G12">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1347,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="G13">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
@@ -1361,21 +1374,21 @@
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>3</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
       </c>
       <c r="E14">
         <v>67</v>
@@ -1384,26 +1397,26 @@
         <v>91</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1415,29 +1428,29 @@
         <v>94</v>
       </c>
       <c r="G15">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>419</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>210</v>
@@ -1446,29 +1459,29 @@
         <v>128</v>
       </c>
       <c r="G16">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="I16">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>570</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>19</v>
@@ -1481,25 +1494,25 @@
       </c>
       <c r="I17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>152</v>
@@ -1508,29 +1521,29 @@
         <v>102</v>
       </c>
       <c r="G18">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="I18">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>427</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>117</v>
@@ -1539,54 +1552,54 @@
         <v>86</v>
       </c>
       <c r="G19">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I19">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>303</v>
       </c>
       <c r="F20">
-        <v>90</v>
+        <v>282</v>
       </c>
       <c r="G20">
-        <v>187</v>
+        <v>296</v>
       </c>
       <c r="I20">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -1598,32 +1611,32 @@
         <v>95</v>
       </c>
       <c r="F21">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I21">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>135</v>
@@ -1632,29 +1645,29 @@
         <v>84</v>
       </c>
       <c r="G22">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>337</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>136</v>
@@ -1663,60 +1676,60 @@
         <v>146</v>
       </c>
       <c r="G23">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="I24">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>199</v>
@@ -1725,18 +1738,18 @@
         <v>155</v>
       </c>
       <c r="G25">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>408</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1744,38 +1757,38 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="I26">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1787,18 +1800,18 @@
         <v>125</v>
       </c>
       <c r="G27">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="I27">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1812,13 +1825,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F28">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G28">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I28">
         <f t="shared" si="0"/>
@@ -1826,10 +1839,10 @@
       </c>
       <c r="J28">
         <f t="shared" si="1"/>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1843,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F29">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="G29">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="I29">
         <f t="shared" si="0"/>
@@ -1857,10 +1870,10 @@
       </c>
       <c r="J29">
         <f t="shared" si="1"/>
-        <v>439</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1874,13 +1887,13 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F30">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G30">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="I30">
         <f t="shared" si="0"/>
@@ -1888,10 +1901,10 @@
       </c>
       <c r="J30">
         <f t="shared" si="1"/>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1905,13 +1918,13 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="F31">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="G31">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="I31">
         <f t="shared" si="0"/>
@@ -1919,10 +1932,10 @@
       </c>
       <c r="J31">
         <f t="shared" si="1"/>
-        <v>926</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1936,13 +1949,13 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="F32">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="G32">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="I32">
         <f t="shared" si="0"/>
@@ -1950,10 +1963,10 @@
       </c>
       <c r="J32">
         <f t="shared" si="1"/>
-        <v>926</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1967,13 +1980,13 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="F33">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="G33">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -1981,21 +1994,21 @@
       </c>
       <c r="J33">
         <f t="shared" si="1"/>
-        <v>926</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
         <v>3</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
       </c>
       <c r="E34">
         <v>18</v>
@@ -2004,29 +2017,29 @@
         <v>73</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>43</v>
@@ -2035,29 +2048,29 @@
         <v>189</v>
       </c>
       <c r="G35">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <f t="shared" si="1"/>
-        <v>297</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>92</v>
@@ -2066,29 +2079,29 @@
         <v>86</v>
       </c>
       <c r="G36">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="I36">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <f t="shared" si="1"/>
-        <v>356</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>44</v>
@@ -2097,15 +2110,15 @@
         <v>23</v>
       </c>
       <c r="G37">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I37">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <f t="shared" si="1"/>
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
